--- a/Расчет справедливой стоимости.xlsx
+++ b/Расчет справедливой стоимости.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
-  <workbookPr/>
+  <workbookPr codeName="ЭтаКнига"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\The Experts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188F233D-BEF2-4143-9889-97CE9E3E03BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83B8ED1-FC94-42CB-96C9-2A674D210FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -286,18 +286,9 @@
     <t>К дисконтирования</t>
   </si>
   <si>
-    <t>PV FCF</t>
-  </si>
-  <si>
-    <t>Сумм PV FCF</t>
-  </si>
-  <si>
     <t>FCF в последний год (2035)</t>
   </si>
   <si>
-    <t>PV TV</t>
-  </si>
-  <si>
     <t>Год</t>
   </si>
   <si>
@@ -305,12 +296,25 @@
   </si>
   <si>
     <t>EV</t>
+  </si>
+  <si>
+    <t>DCF</t>
+  </si>
+  <si>
+    <t>CUM_DCF</t>
+  </si>
+  <si>
+    <t>DTV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.000%"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -384,7 +388,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -405,6 +409,10 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -685,6 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Лист1"/>
   <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1191,14 +1200,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0747CB50-B0C8-4AF7-B722-9CB9C2820A41}">
-  <dimension ref="A1:L31"/>
+  <sheetPr codeName="Лист2"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44" bestFit="1" customWidth="1"/>
     <col min="2" max="12" width="12.109375" customWidth="1"/>
+    <col min="14" max="14" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>74</v>
       </c>
@@ -1206,7 +1220,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>76</v>
       </c>
@@ -1214,39 +1228,51 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>77</v>
       </c>
       <c r="B3" s="9">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="13"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>78</v>
       </c>
       <c r="B4" s="9">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="13"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>79</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O5" s="14"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="15"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>80</v>
       </c>
       <c r="B6" s="10">
         <v>46112</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O6" s="14"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="15"/>
+    </row>
+    <row r="7" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>0</v>
       </c>
@@ -1283,8 +1309,11 @@
       <c r="L7" s="8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="13"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>68</v>
       </c>
@@ -1321,8 +1350,10 @@
       <c r="L8" s="2">
         <v>37.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="O8" s="9"/>
+      <c r="Q8" s="13"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>72</v>
       </c>
@@ -1357,8 +1388,9 @@
       <c r="L9" s="2">
         <v>0.06</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="Q9" s="13"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>30</v>
       </c>
@@ -1396,7 +1428,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>73</v>
       </c>
@@ -1434,7 +1466,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>47</v>
       </c>
@@ -1472,7 +1504,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>73</v>
       </c>
@@ -1510,7 +1542,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>52</v>
       </c>
@@ -1548,7 +1580,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>69</v>
       </c>
@@ -1586,7 +1618,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>70</v>
       </c>
@@ -1738,228 +1770,229 @@
         <v>0.02</v>
       </c>
     </row>
+    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12">
+        <f>C14+C12-C16-C18</f>
+        <v>2.8</v>
+      </c>
+      <c r="D20" s="12">
+        <f t="shared" ref="C20:L20" si="0">D14+D12-D16-D18</f>
+        <v>3.9000000000000004</v>
+      </c>
+      <c r="E20" s="12">
+        <f t="shared" si="0"/>
+        <v>5.3</v>
+      </c>
+      <c r="F20" s="12">
+        <f t="shared" si="0"/>
+        <v>6.9999999999999991</v>
+      </c>
+      <c r="G20" s="12">
+        <f t="shared" si="0"/>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H20" s="12">
+        <f t="shared" si="0"/>
+        <v>9.6000000000000014</v>
+      </c>
+      <c r="I20" s="12">
+        <f t="shared" si="0"/>
+        <v>10.600000000000001</v>
+      </c>
+      <c r="J20" s="12">
+        <f t="shared" si="0"/>
+        <v>11.400000000000002</v>
+      </c>
+      <c r="K20" s="12">
+        <f t="shared" si="0"/>
+        <v>12.4</v>
+      </c>
+      <c r="L20" s="12">
+        <f t="shared" si="0"/>
+        <v>13.1</v>
+      </c>
+    </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C21">
-        <f>C14+C12-C16-C18</f>
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="D21">
-        <f>D14+D12-D16-D18</f>
-        <v>3.9000000000000004</v>
+        <f>C21+1</f>
+        <v>1.5</v>
       </c>
       <c r="E21">
-        <f>E14+E12-E16-E18</f>
-        <v>5.3</v>
+        <f t="shared" ref="E21:L21" si="1">D21+1</f>
+        <v>2.5</v>
       </c>
       <c r="F21">
-        <f t="shared" ref="F21:L21" si="0">F14+F12-F16-F18</f>
-        <v>6.9999999999999991</v>
+        <f t="shared" si="1"/>
+        <v>3.5</v>
       </c>
       <c r="G21">
-        <f t="shared" si="0"/>
-        <v>8.8000000000000007</v>
+        <f t="shared" si="1"/>
+        <v>4.5</v>
       </c>
       <c r="H21">
-        <f t="shared" si="0"/>
-        <v>9.6000000000000014</v>
+        <f t="shared" si="1"/>
+        <v>5.5</v>
       </c>
       <c r="I21">
-        <f t="shared" si="0"/>
-        <v>10.600000000000001</v>
+        <f t="shared" si="1"/>
+        <v>6.5</v>
       </c>
       <c r="J21">
-        <f t="shared" si="0"/>
-        <v>11.400000000000002</v>
+        <f t="shared" si="1"/>
+        <v>7.5</v>
       </c>
       <c r="K21">
-        <f t="shared" si="0"/>
-        <v>12.4</v>
+        <f t="shared" si="1"/>
+        <v>8.5</v>
       </c>
       <c r="L21">
-        <f t="shared" si="0"/>
-        <v>13.1</v>
+        <f t="shared" si="1"/>
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="11">
+        <f>1/(1+$B$2)^C21</f>
+        <v>0.9128709291752769</v>
+      </c>
+      <c r="D22" s="11">
+        <f t="shared" ref="D22:L22" si="2">1/(1+$B$2)^D21</f>
+        <v>0.7607257743127307</v>
+      </c>
+      <c r="E22" s="11">
+        <f t="shared" si="2"/>
+        <v>0.63393814526060899</v>
+      </c>
+      <c r="F22" s="11">
+        <f t="shared" si="2"/>
+        <v>0.52828178771717416</v>
+      </c>
+      <c r="G22" s="11">
+        <f t="shared" si="2"/>
+        <v>0.44023482309764517</v>
+      </c>
+      <c r="H22" s="11">
+        <f t="shared" si="2"/>
+        <v>0.36686235258137107</v>
+      </c>
+      <c r="I22" s="11">
+        <f t="shared" si="2"/>
+        <v>0.30571862715114251</v>
+      </c>
+      <c r="J22" s="11">
+        <f t="shared" si="2"/>
+        <v>0.25476552262595203</v>
+      </c>
+      <c r="K22" s="11">
+        <f t="shared" si="2"/>
+        <v>0.21230460218829345</v>
+      </c>
+      <c r="L22" s="11">
+        <f>1/(1+$B$2)^L21</f>
+        <v>0.17692050182357785</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>87</v>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <f>C23+1</f>
-        <v>2</v>
-      </c>
-      <c r="E23">
-        <f t="shared" ref="E23:L23" si="1">D23+1</f>
-        <v>3</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="I23">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="L23">
-        <f t="shared" si="1"/>
-        <v>10</v>
+      <c r="C23" s="11">
+        <f>C20*C22</f>
+        <v>2.556038601690775</v>
+      </c>
+      <c r="D23" s="11">
+        <f t="shared" ref="C23:L23" si="3">D20*D22</f>
+        <v>2.9668305198196498</v>
+      </c>
+      <c r="E23" s="11">
+        <f t="shared" si="3"/>
+        <v>3.3598721698812275</v>
+      </c>
+      <c r="F23" s="11">
+        <f t="shared" si="3"/>
+        <v>3.6979725140202184</v>
+      </c>
+      <c r="G23" s="11">
+        <f t="shared" si="3"/>
+        <v>3.8740664432592777</v>
+      </c>
+      <c r="H23" s="11">
+        <f t="shared" si="3"/>
+        <v>3.5218785847811627</v>
+      </c>
+      <c r="I23" s="11">
+        <f t="shared" si="3"/>
+        <v>3.2406174478021108</v>
+      </c>
+      <c r="J23" s="11">
+        <f t="shared" si="3"/>
+        <v>2.9043269579358539</v>
+      </c>
+      <c r="K23" s="11">
+        <f t="shared" si="3"/>
+        <v>2.632577067134839</v>
+      </c>
+      <c r="L23" s="11">
+        <f>L20*L22</f>
+        <v>2.31765857388887</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="11">
-        <f>1/(1+$B$2)^C23</f>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D24" s="11">
-        <f t="shared" ref="D24:L24" si="2">1/(1+$B$2)^D23</f>
-        <v>0.69444444444444442</v>
-      </c>
-      <c r="E24" s="11">
-        <f t="shared" si="2"/>
-        <v>0.57870370370370372</v>
-      </c>
-      <c r="F24" s="11">
-        <f t="shared" si="2"/>
-        <v>0.48225308641975312</v>
-      </c>
-      <c r="G24" s="11">
-        <f t="shared" si="2"/>
-        <v>0.4018775720164609</v>
-      </c>
-      <c r="H24" s="11">
-        <f t="shared" si="2"/>
-        <v>0.33489797668038412</v>
-      </c>
-      <c r="I24" s="11">
-        <f t="shared" si="2"/>
-        <v>0.27908164723365342</v>
-      </c>
-      <c r="J24" s="11">
-        <f t="shared" si="2"/>
-        <v>0.23256803936137788</v>
-      </c>
-      <c r="K24" s="11">
-        <f t="shared" si="2"/>
-        <v>0.1938066994678149</v>
-      </c>
-      <c r="L24" s="11">
-        <f t="shared" si="2"/>
-        <v>0.16150558288984573</v>
+        <v>88</v>
+      </c>
+      <c r="B24" s="11">
+        <f>SUM(C23:L23)</f>
+        <v>31.071838880213988</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="11">
-        <f>C21*C24</f>
-        <v>2.3333333333333335</v>
-      </c>
-      <c r="D25" s="11">
-        <f t="shared" ref="D25:L25" si="3">D21*D24</f>
-        <v>2.7083333333333335</v>
-      </c>
-      <c r="E25" s="11">
-        <f t="shared" si="3"/>
-        <v>3.0671296296296298</v>
-      </c>
-      <c r="F25" s="11">
-        <f t="shared" si="3"/>
-        <v>3.3757716049382713</v>
-      </c>
-      <c r="G25" s="11">
-        <f t="shared" si="3"/>
-        <v>3.5365226337448563</v>
-      </c>
-      <c r="H25" s="11">
-        <f t="shared" si="3"/>
-        <v>3.2150205761316881</v>
-      </c>
-      <c r="I25" s="11">
-        <f t="shared" si="3"/>
-        <v>2.9582654606767265</v>
-      </c>
-      <c r="J25" s="11">
-        <f t="shared" si="3"/>
-        <v>2.6512756487197082</v>
-      </c>
-      <c r="K25" s="11">
-        <f t="shared" si="3"/>
-        <v>2.4032030734009049</v>
-      </c>
-      <c r="L25" s="11">
-        <f t="shared" si="3"/>
-        <v>2.115723135856979</v>
+      <c r="B25" s="11">
+        <f>L20*(1+B3)</f>
+        <v>13.624000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="11">
+        <f>B25*(1+$B$3)/($B$2-$B$3)</f>
+        <v>88.555999999999997</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B27" s="11">
-        <f>SUM(C25:L25)</f>
-        <v>28.364578429765434</v>
+        <f>B26/(1+$B$2)^10</f>
+        <v>14.302288398393179</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B28" s="11">
-        <f>L21</f>
-        <v>13.1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>88</v>
-      </c>
-      <c r="B29" s="11">
-        <f>B28*(1+$B$3)/($B$2-$B$3)</f>
-        <v>85.15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>86</v>
-      </c>
-      <c r="B30" s="11">
-        <f>B29/(1+$B$2)^10</f>
-        <v>13.752200383070367</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>89</v>
-      </c>
-      <c r="B31" s="11">
-        <f>B27+B30</f>
-        <v>42.116778812835804</v>
+        <f>B24+B27</f>
+        <v>45.374127278607169</v>
       </c>
     </row>
   </sheetData>
